--- a/input/Test Data_ Subjects.xlsx
+++ b/input/Test Data_ Subjects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25219"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\lunar-bloom\forks\nimendoza\B2023-R3X-07\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\neomi\forks\nimendoza\B2023-R3X-07\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8517118-A6B5-4E20-9350-2EFD3ACAD1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2834C0B7-B96E-4CFC-A5D9-2FAE6E1FBC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shifts" sheetId="1" r:id="rId1"/>
@@ -608,13 +608,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -631,13 +631,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -2054,6 +2054,9 @@
     </row>
   </sheetData>
   <mergeCells count="160">
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="Q11:S11"/>
     <mergeCell ref="T13:V13"/>
     <mergeCell ref="W13:Y13"/>
     <mergeCell ref="B12:D12"/>
@@ -2065,13 +2068,24 @@
     <mergeCell ref="Q13:S13"/>
     <mergeCell ref="Q12:S12"/>
     <mergeCell ref="T12:V12"/>
-    <mergeCell ref="T11:V11"/>
-    <mergeCell ref="W11:Y11"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="W12:Y12"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="W9:Y9"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="W11:Y11"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="T8:V8"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="K10:M10"/>
@@ -2083,20 +2097,6 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="W9:Y9"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="T8:V8"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="E8:G8"/>
@@ -2127,6 +2127,14 @@
     <mergeCell ref="K21:M21"/>
     <mergeCell ref="N21:P21"/>
     <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
     <mergeCell ref="T4:V4"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T5:V5"/>
@@ -2175,18 +2183,10 @@
     <mergeCell ref="Q18:S18"/>
     <mergeCell ref="T18:V18"/>
     <mergeCell ref="W18:Y18"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K19:M19"/>
     <mergeCell ref="N19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="W17:Y17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="N17:P17"/>

--- a/input/Test Data_ Subjects.xlsx
+++ b/input/Test Data_ Subjects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\neomi\forks\nimendoza\B2023-R3X-07\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2834C0B7-B96E-4CFC-A5D9-2FAE6E1FBC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DCB7F7-9F50-447E-9FB4-9B2BB7C552FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -700,10 +700,10 @@
         <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2">
         <v>8</v>
@@ -723,10 +723,10 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2">
         <v>8</v>
@@ -746,10 +746,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2">
         <v>8</v>
@@ -769,10 +769,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2">
         <v>8</v>
@@ -792,10 +792,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2">
         <v>8</v>
@@ -815,10 +815,10 @@
         <v>5</v>
       </c>
       <c r="D11" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
@@ -838,10 +838,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2">
         <v>8</v>
@@ -861,10 +861,10 @@
         <v>5</v>
       </c>
       <c r="D13" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F13" s="2">
         <v>8</v>
@@ -884,10 +884,10 @@
         <v>5</v>
       </c>
       <c r="D14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2">
         <v>8</v>
@@ -907,10 +907,10 @@
         <v>5</v>
       </c>
       <c r="D15" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2">
         <v>8</v>

--- a/input/Test Data_ Subjects.xlsx
+++ b/input/Test Data_ Subjects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\neomi\forks\nimendoza\B2023-R3X-07\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\lunar-bloom\forks\nimendoza\B2023-R3X-07\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DCB7F7-9F50-447E-9FB4-9B2BB7C552FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326BCC7E-AE08-423D-AEF0-9685508C7259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shifts" sheetId="1" r:id="rId1"/>

--- a/input/Test Data_ Subjects.xlsx
+++ b/input/Test Data_ Subjects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\lunar-bloom\forks\nimendoza\B2023-R3X-07\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B82171A-3295-461A-B49B-3F6AFD0D452C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FB850B-4708-4813-A8C8-A97ECD89BC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -795,7 +795,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -812,7 +812,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -829,7 +829,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="2">
-        <v>8</v>
+        <v>999</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -846,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="2">
-        <v>8</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2234,25 +2234,123 @@
     </row>
   </sheetData>
   <mergeCells count="160">
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="W13:Y13"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="W12:Y12"/>
+    <mergeCell ref="W16:Y16"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="W14:Y14"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="W15:Y15"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="W19:Y19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="W20:Y20"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="W18:Y18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="W21:Y21"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="W8:Y8"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="W6:Y6"/>
     <mergeCell ref="T9:V9"/>
     <mergeCell ref="W9:Y9"/>
     <mergeCell ref="T11:V11"/>
@@ -2277,123 +2375,25 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="H11:J11"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="W7:Y7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="W8:Y8"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="T21:V21"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="W17:Y17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="T4:V4"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="T5:V5"/>
-    <mergeCell ref="W5:Y5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="W19:Y19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="W20:Y20"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="W18:Y18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="W16:Y16"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="W14:Y14"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="W15:Y15"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="W12:Y12"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:Y21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
